--- a/Dear Data Project.xlsx
+++ b/Dear Data Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b95d8631791e2324/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b95d8631791e2324/Documents/GitHub/Uni Dear Data project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0588B67A-6D48-4657-A006-E81CCB2FAF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9935FD9-07A9-443C-9DE2-7A9186B23C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BC70F7DF-126F-41EC-B103-592603286880}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
   <si>
     <t>Perfume name</t>
   </si>
@@ -53,15 +53,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Scent</t>
-  </si>
-  <si>
-    <t>Longevity</t>
-  </si>
-  <si>
-    <t>Projection</t>
-  </si>
-  <si>
     <t>Arabians Tonka</t>
   </si>
   <si>
@@ -125,9 +116,6 @@
     <t>Le male Elixir</t>
   </si>
   <si>
-    <t>Jean Paul Gaultier Eau de Parfum 17/10/2026                    8</t>
-  </si>
-  <si>
     <t>Ombre Nomad</t>
   </si>
   <si>
@@ -140,9 +128,6 @@
     <t>Atlantis</t>
   </si>
   <si>
-    <t>French Avenue Extrait de Parfum 17/10/2026                     9.5                 8</t>
-  </si>
-  <si>
     <t>Erba Gold</t>
   </si>
   <si>
@@ -191,7 +176,10 @@
     <t>33 White</t>
   </si>
   <si>
-    <t>Versatility</t>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>JPG</t>
   </si>
 </sst>
 </file>
@@ -568,13 +556,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAC8709-5BAE-4D99-8958-3F3E68D8F90C}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -587,643 +575,421 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1">
         <v>46311</v>
       </c>
-      <c r="G2">
-        <v>10</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1">
         <v>46311</v>
       </c>
-      <c r="G3">
-        <v>8.5</v>
-      </c>
-      <c r="H3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1">
         <v>46311</v>
       </c>
-      <c r="G4">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
         <v>46311</v>
       </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>8.5</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1">
         <v>46311</v>
       </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1">
         <v>46311</v>
       </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1">
         <v>46311</v>
       </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1">
         <v>46311</v>
       </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1">
         <v>46311</v>
       </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1">
         <v>46311</v>
       </c>
-      <c r="G11">
-        <v>8</v>
-      </c>
-      <c r="H11">
-        <v>8</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
       </c>
       <c r="F12" s="1">
         <v>46312</v>
       </c>
-      <c r="G12">
-        <v>7</v>
-      </c>
-      <c r="H12">
-        <v>8</v>
-      </c>
-      <c r="I12">
-        <v>8</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1">
         <v>46312</v>
       </c>
-      <c r="G13">
-        <v>9</v>
-      </c>
-      <c r="H13">
-        <v>8</v>
-      </c>
-      <c r="I13">
-        <v>8</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14">
-        <v>8</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1">
         <v>46312</v>
       </c>
-      <c r="G15">
-        <v>7</v>
-      </c>
-      <c r="H15">
-        <v>7</v>
-      </c>
-      <c r="I15">
-        <v>7</v>
-      </c>
-      <c r="J15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1">
         <v>46312</v>
       </c>
-      <c r="G16">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
-      <c r="I16">
-        <v>6</v>
-      </c>
-      <c r="J16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17">
-        <v>8</v>
-      </c>
-      <c r="J17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G18">
-        <v>8</v>
-      </c>
-      <c r="H18">
-        <v>8</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
-      <c r="J18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G19">
-        <v>7</v>
-      </c>
-      <c r="H19">
-        <v>7</v>
-      </c>
-      <c r="I19">
-        <v>7</v>
-      </c>
-      <c r="J19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G20">
-        <v>8</v>
-      </c>
-      <c r="H20">
-        <v>8</v>
-      </c>
-      <c r="I20">
-        <v>8</v>
-      </c>
-      <c r="J20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G21">
-        <v>9.5</v>
-      </c>
-      <c r="H21">
-        <v>9</v>
-      </c>
-      <c r="I21">
-        <v>9</v>
-      </c>
-      <c r="J21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G22">
-        <v>10</v>
-      </c>
-      <c r="H22">
-        <v>9</v>
-      </c>
-      <c r="I22">
-        <v>9</v>
-      </c>
-      <c r="J22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G23">
-        <v>8</v>
-      </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>8</v>
-      </c>
-      <c r="I24">
-        <v>8</v>
-      </c>
-      <c r="J24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G25">
-        <v>8</v>
-      </c>
-      <c r="H25">
-        <v>9</v>
-      </c>
-      <c r="I25">
-        <v>9</v>
-      </c>
-      <c r="J25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46312</v>
-      </c>
-      <c r="G26">
-        <v>8.5</v>
-      </c>
-      <c r="H26">
-        <v>9</v>
-      </c>
-      <c r="I26">
-        <v>9</v>
-      </c>
-      <c r="J26">
-        <v>7</v>
-      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E802F14A90D1B345818A6FFB06D8A03D" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ea7226ff09ef22af6f5ba21dc65cff36">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="75eb23ce-bee3-4614-ac9d-e7493ba98713" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="807d9844cc6c643302a5e086dcc98a76" ns3:_="">
     <xsd:import namespace="75eb23ce-bee3-4614-ac9d-e7493ba98713"/>
@@ -1367,15 +1133,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1383,6 +1140,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C15603D6-4B0C-40C1-B20B-6EDC4D5CF7F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E657AE7E-2EF5-4D66-BC10-8589A15A9EA7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1400,26 +1165,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C15603D6-4B0C-40C1-B20B-6EDC4D5CF7F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{121902D1-ECA7-4843-8A68-51E4DF37F24F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="75eb23ce-bee3-4614-ac9d-e7493ba98713"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75eb23ce-bee3-4614-ac9d-e7493ba98713"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>